--- a/Team-Data/2012-13/11-8-2012-13.xlsx
+++ b/Team-Data/2012-13/11-8-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -742,13 +809,13 @@
         <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>7</v>
@@ -763,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -784,10 +851,10 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU2" t="n">
         <v>12</v>
@@ -811,7 +878,7 @@
         <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>4</v>
@@ -942,7 +1009,7 @@
         <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -951,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
@@ -969,22 +1036,22 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>6</v>
@@ -993,7 +1060,7 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1176,7 @@
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
         <v>25</v>
@@ -1118,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
         <v>26</v>
@@ -1127,13 +1194,13 @@
         <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>14</v>
@@ -1172,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1358,7 @@
         <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
@@ -1303,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1312,28 +1379,28 @@
         <v>16</v>
       </c>
       <c r="AM5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN5" t="n">
         <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP5" t="n">
         <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
         <v>29</v>
       </c>
       <c r="AT5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU5" t="n">
         <v>19</v>
@@ -1345,7 +1412,7 @@
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>26</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -1389,106 +1456,106 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>80.8</v>
+        <v>80</v>
       </c>
       <c r="K6" t="n">
-        <v>0.448</v>
+        <v>0.456</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.281</v>
+        <v>0.262</v>
       </c>
       <c r="O6" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.768</v>
       </c>
       <c r="R6" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="T6" t="n">
-        <v>42.4</v>
+        <v>42.8</v>
       </c>
       <c r="U6" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="V6" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.2</v>
+        <v>24.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,53 +1564,53 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
       </c>
       <c r="AS6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW6" t="n">
         <v>14</v>
       </c>
-      <c r="AT6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4</v>
       </c>
-      <c r="AV6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7</v>
-      </c>
       <c r="BD6" t="n">
         <v>10</v>
       </c>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1716,22 @@
         <v>-5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
         <v>7</v>
       </c>
       <c r="AI7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>15</v>
@@ -1691,13 +1758,13 @@
         <v>30</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
         <v>18</v>
@@ -1721,10 +1788,10 @@
         <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1867,25 +1934,25 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>25</v>
       </c>
       <c r="AR8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2013,25 +2080,25 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>19</v>
@@ -2040,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="AM9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN9" t="n">
         <v>26</v>
@@ -2079,13 +2146,13 @@
         <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-11</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>29</v>
@@ -2210,7 +2277,7 @@
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ10" t="n">
         <v>21</v>
@@ -2225,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>10</v>
@@ -2234,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
@@ -2246,13 +2313,13 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>10</v>
@@ -2392,13 +2459,13 @@
         <v>7</v>
       </c>
       <c r="AI11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ11" t="n">
         <v>19</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>21</v>
@@ -2413,19 +2480,19 @@
         <v>8</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR11" t="n">
         <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>13</v>
@@ -2440,7 +2507,7 @@
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>25</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
@@ -2577,7 +2644,7 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>27</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
         <v>2</v>
@@ -2610,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2631,7 +2698,7 @@
         <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC12" t="n">
         <v>14</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2808,22 @@
         <v>-3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>12</v>
@@ -2798,7 +2865,7 @@
         <v>29</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -2845,100 +2912,100 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
         <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>0.502</v>
+        <v>0.496</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="P14" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.774</v>
       </c>
       <c r="R14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="T14" t="n">
-        <v>39.5</v>
+        <v>38.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="V14" t="n">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="W14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Y14" t="n">
         <v>3.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="AA14" t="n">
         <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.3</v>
+        <v>104.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>7</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
         <v>27</v>
@@ -2947,58 +3014,58 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM14" t="n">
         <v>13</v>
       </c>
-      <c r="AM14" t="n">
-        <v>17</v>
-      </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA14" t="n">
         <v>8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3162,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
         <v>20</v>
@@ -3174,10 +3241,10 @@
         <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -3323,13 +3390,13 @@
         <v>2</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
         <v>5</v>
@@ -3341,7 +3408,7 @@
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
@@ -3353,7 +3420,7 @@
         <v>27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>10.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3505,10 +3572,10 @@
         <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3520,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3721,13 @@
         <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF18" t="n">
         <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
@@ -3672,13 +3739,13 @@
         <v>10</v>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL18" t="n">
         <v>8</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN18" t="n">
         <v>6</v>
@@ -3699,19 +3766,19 @@
         <v>15</v>
       </c>
       <c r="AT18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY18" t="n">
         <v>3</v>
@@ -3723,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF19" t="n">
         <v>2</v>
@@ -3869,7 +3936,7 @@
         <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
@@ -3878,19 +3945,19 @@
         <v>6</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV19" t="n">
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4045,7 +4112,7 @@
         <v>25</v>
       </c>
       <c r="AN20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
@@ -4063,7 +4130,7 @@
         <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
@@ -4075,7 +4142,7 @@
         <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4267,7 @@
         <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF21" t="n">
         <v>1</v>
@@ -4236,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR21" t="n">
         <v>22</v>
@@ -4245,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4301,100 +4368,100 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="J22" t="n">
-        <v>74.2</v>
+        <v>74.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.464</v>
+        <v>0.456</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.407</v>
+        <v>0.411</v>
       </c>
       <c r="O22" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.841</v>
+        <v>0.82</v>
       </c>
       <c r="R22" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
-        <v>34.8</v>
+        <v>36</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>44.5</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="W22" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="X22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>98</v>
+        <v>98.3</v>
       </c>
       <c r="AC22" t="n">
         <v>5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4403,10 +4470,10 @@
         <v>8</v>
       </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="n">
         <v>5</v>
@@ -4418,25 +4485,25 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AR22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>4</v>
@@ -4445,16 +4512,16 @@
         <v>1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4561,16 +4628,16 @@
         <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
         <v>7</v>
@@ -4600,7 +4667,7 @@
         <v>25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>16</v>
@@ -4609,7 +4676,7 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
         <v>11</v>
@@ -4618,7 +4685,7 @@
         <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
         <v>18</v>
@@ -4627,13 +4694,13 @@
         <v>27</v>
       </c>
       <c r="AZ23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
         <v>7</v>
@@ -4785,7 +4852,7 @@
         <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>-7.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH25" t="n">
         <v>7</v>
@@ -4943,7 +5010,7 @@
         <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK25" t="n">
         <v>21</v>
@@ -4952,16 +5019,16 @@
         <v>21</v>
       </c>
       <c r="AM25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN25" t="n">
         <v>23</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>24</v>
@@ -4970,7 +5037,7 @@
         <v>3</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>6</v>
@@ -4979,16 +5046,16 @@
         <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>1</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
@@ -4997,7 +5064,7 @@
         <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -5029,133 +5096,133 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>37.3</v>
       </c>
       <c r="J26" t="n">
-        <v>86.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.418</v>
+        <v>0.416</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.732</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="S26" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>43.8</v>
       </c>
       <c r="U26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>-6</v>
+        <v>-4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT26" t="n">
         <v>12</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>25</v>
@@ -5164,25 +5231,25 @@
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
         <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH27" t="n">
         <v>1</v>
@@ -5307,7 +5374,7 @@
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>25</v>
@@ -5316,7 +5383,7 @@
         <v>25</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN27" t="n">
         <v>22</v>
@@ -5328,16 +5395,16 @@
         <v>23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5349,7 +5416,7 @@
         <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
         <v>30</v>
@@ -5364,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5486,7 +5553,7 @@
         <v>7</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>24</v>
@@ -5501,7 +5568,7 @@
         <v>18</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO28" t="n">
         <v>22</v>
@@ -5516,16 +5583,16 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT28" t="n">
         <v>28</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>11</v>
@@ -5543,7 +5610,7 @@
         <v>16</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
@@ -5677,7 +5744,7 @@
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM29" t="n">
         <v>9</v>
@@ -5692,7 +5759,7 @@
         <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR29" t="n">
         <v>15</v>
@@ -5701,10 +5768,10 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5719,13 +5786,13 @@
         <v>24</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>21</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
@@ -5862,43 +5929,43 @@
         <v>20</v>
       </c>
       <c r="AM30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN30" t="n">
         <v>14</v>
       </c>
       <c r="AO30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP30" t="n">
         <v>16</v>
       </c>
-      <c r="AP30" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
         <v>20</v>
       </c>
       <c r="AV30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
@@ -5907,7 +5974,7 @@
         <v>21</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6035,13 +6102,13 @@
         <v>22</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM31" t="n">
         <v>3</v>
@@ -6065,7 +6132,7 @@
         <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
@@ -6077,7 +6144,7 @@
         <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-8-2012-13</t>
+          <t>2012-11-08</t>
         </is>
       </c>
     </row>
